--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T10:38:49+00:00</t>
+    <t>2025-02-11T11:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:03:37+00:00</t>
+    <t>2025-02-11T12:08:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -660,7 +660,8 @@
     <t>FR Core Observation Level Of Exertion Extension</t>
   </si>
   <si>
-    <t>French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure | Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort)</t>
+    <t>Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort).
+French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -680,7 +681,8 @@
     <t>FR Core Observation Body Position Ext Extension</t>
   </si>
   <si>
-    <t>CIMI extension (in FHIR R4) defined in the context of the Respiratory Rate profile. This extension is used to specify the body position during the respiratory rate observation | Extension CIMI (upgardée en FHIR R4) définie dans le contexte du profil Respiratory rate. Cette extension permet de préciser la position du corps lors de la mesure de la fréquence respiratoire.</t>
+    <t>Extension CIMI (upgardée en FHIR R4) définie dans le contexte du profil Respiratory rate. Cette extension permet de préciser la position du corps lors de la mesure de la fréquence respiratoire.
+CIMI extension (in FHIR R4) defined in the context of the Respiratory Rate profile. This extension is used to specify the body position during the respiratory rate observation</t>
   </si>
   <si>
     <t>Observation.extension:supportingInfo</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:08:53+00:00</t>
+    <t>2025-02-11T15:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:31:42+00:00</t>
+    <t>2025-02-11T17:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:07:06+00:00</t>
+    <t>2025-02-11T17:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:08:15+00:00</t>
+    <t>2025-02-11T17:29:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
